--- a/deliverables/SYLTHARAE-Pro_Work_History_and_Task_Register.xlsx
+++ b/deliverables/SYLTHARAE-Pro_Work_History_and_Task_Register.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -104,16 +104,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C2A1F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -185,11 +180,6 @@
         <fgColor rgb="00DEE8F8"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FBE3E0"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -217,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -300,13 +290,10 @@
     <xf numFmtId="0" fontId="12" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -5212,7 +5199,7 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="96.2" customHeight="1">
+    <row r="92" ht="134" customHeight="1">
       <c r="A92" s="17" t="inlineStr">
         <is>
           <t>Repair the test broken by this round's action renaming</t>
@@ -5233,14 +5220,14 @@
           <t>11. Open work: unfinished, blocked or never attempted</t>
         </is>
       </c>
-      <c r="E92" s="23" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="F92" s="28" t="inlineStr">
-        <is>
-          <t>Urgent</t>
+      <c r="E92" s="14" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F92" s="15" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="G92" s="19" t="inlineStr">
@@ -5248,17 +5235,15 @@
           <t>11.0 Stage: open work carried forward</t>
         </is>
       </c>
-      <c r="H92" s="24" t="n">
-        <v>46320</v>
-      </c>
-      <c r="I92" s="25" t="inlineStr">
-        <is>
-          <t>Unverified</t>
-        </is>
+      <c r="H92" s="20" t="n">
+        <v>46320</v>
+      </c>
+      <c r="I92" s="20" t="n">
+        <v>46320</v>
       </c>
       <c r="J92" s="19" t="inlineStr">
         <is>
-          <t>One test is newly failing because of this round's own work. It insists on a specific line of code that published a select-all action under an old name, and that line was replaced when action names were given single owners. One of the two must give way: either the control keeps publishing under the old name, or the test checks the behaviour - that the name resolves and that clicking it selects - instead of the text of an assignment. This is the only failure the round introduced, and it is marked urgent because it belongs in the review that is waiting for the owner, not in a later round.</t>
+          <t>One test was newly failing because of this round's own work. It insisted on a specific line of code that published a select-all action under an old name, and that line had been replaced when action names were given single owners. The product behaviour was correct and was left alone: the files screen owns the name and the shared module exports its copy under a suffix that the control using it names explicitly. The test was the stale side, so it now checks the ownership rule instead of the text of one assignment - the suffixed export exists, the shared module does not claim the name the screen owns, and the control that uses the shared copy names it - which is stricter than what it replaced. It was shown failing before the change and passing after it, in five passing tests with three skipped for lack of a JavaScript runtime, alongside the ten action-ownership tests.</t>
         </is>
       </c>
     </row>
@@ -5982,280 +5967,280 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="28" t="inlineStr">
         <is>
           <t>HOW TO READ THIS REGISTER</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>What this workbook is</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>It is a record of work done on one software product between 23 and 25 October 2026, written so that a reader who knows nothing about software can follow it. Each task says what was wrong, what was done about it and what was checked afterwards. Nothing in it requires another file to be understood.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>It is not a plan or a promise: dates are either the day the work actually happened or an amber cell saying the date is not evidenced.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>The status values, and what each one means here</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>Completed - the work is done and was checked afterwards. Used only where a test, a measurement or an observed result exists.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="31" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>Working - started and not finished. The description says exactly how far it got.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="31" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>Pending Review - finished by the person who did it, but not yet read, approved or merged by someone else. It is treated as unapproved until that happens.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="31" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>Open - known, described and not yet started, or stopped deliberately because a decision is needed first.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="31" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>Overdue - not used. Nothing in this record has an agreed due date, so calling a task overdue would invent a commitment nobody made.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="31" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>Template - not used. This register records real work rather than reusable task patterns.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="31" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>Cancelled - not used. Nothing was abandoned after starting; the one task that was stopped is kept as Open for the reason given in its description.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="30" t="inlineStr">
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>The priority values</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="31" t="inlineStr">
-        <is>
-          <t>Urgent - must be settled before the branch under review can be accepted. Used once, for the single test this round broke.</t>
+      <c r="B17" s="30" t="inlineStr">
+        <is>
+          <t>Urgent - must be settled before the branch under review can be accepted. Not used in the final version: the one item that earned it, the single test this round broke, has been repaired and is recorded as completed.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="31" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>High - the work affects whether a person can use the software, whether data can be lost, or whether a claim can be trusted.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="31" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Medium - real defects and real gaps, but with a workaround or a limited blast radius.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="31" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>Low - clean-up, documentation and improvements that do not change whether the software works.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="31" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>Priorities were taken from the severity already assigned when each problem was found, not assigned afresh for this workbook.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="30" t="inlineStr">
+      <c r="B23" s="29" t="inlineStr">
         <is>
           <t>How the dates work</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="31" t="inlineStr">
+      <c r="B24" s="30" t="inlineStr">
         <is>
           <t>Every date in the two date columns falls inside October 2026, and no date is later than 25 October 2026, the day this register was produced.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="31" t="inlineStr">
+      <c r="B25" s="30" t="inlineStr">
         <is>
           <t>A plain date is a real date: the day the work actually started or finished, taken from the project's own history.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="31" t="inlineStr">
+      <c r="B26" s="30" t="inlineStr">
         <is>
           <t>An amber cell reading Unverified is the honest answer that no evidenced date exists. The description says what is missing and, where it can be judged, roughly how much work remains in words rather than in an invented date.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="31" t="inlineStr">
+      <c r="B27" s="30" t="inlineStr">
         <is>
           <t>The work described here began on 23 October 2026. Nothing earlier is claimed, because the project's history contains no earlier record of work.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="31" t="inlineStr">
+      <c r="B28" s="30" t="inlineStr">
         <is>
           <t>For a task that has never been started, the start column shows the day the gap was first recorded as known work, and the end column says Unverified because nothing has been finished and no completion has been agreed.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="30" t="inlineStr">
+      <c r="B30" s="29" t="inlineStr">
         <is>
           <t>How the tasks are organised</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="31" t="inlineStr">
+      <c r="B31" s="30" t="inlineStr">
         <is>
           <t>The eleven numbered rows ending in '.0 Stage:' are stage headings. Each one groups the work of a single stretch of effort, and each child task names its stage in the 'Main Task (Original/Parent)' column.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="31" t="inlineStr">
+      <c r="B32" s="30" t="inlineStr">
         <is>
           <t>The translation feature is a sub-stage inside stage 5, and its eight tasks name it as their parent, so there are three levels in that part of the register.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="31" t="inlineStr">
+      <c r="B33" s="30" t="inlineStr">
         <is>
           <t>The 'Does it fall under a group?' column repeats the stage name on every child row so that a filtered or sorted view stays readable.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="31" t="inlineStr">
+      <c r="B34" s="30" t="inlineStr">
         <is>
           <t>The 'Type' column uses plain words: Development, Testing, Verification, Research, Planning, Measurement, Documentation, Tooling, Setup and Coordination.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="30" t="inlineStr">
+      <c r="B36" s="29" t="inlineStr">
         <is>
           <t>What is covered</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="31" t="inlineStr">
+      <c r="B37" s="30" t="inlineStr">
         <is>
           <t>One hundred and five rows: eleven stage headings, one sub-stage heading, ninety-three individual tasks, covering every piece of work recorded in the project between 23 and 25 October 2026 - research, planning, building, testing, measuring, documenting and coordinating.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="31" t="inlineStr">
-        <is>
-          <t>Seventy-four individual tasks are completed, eighty-five rows in total once the finished stage headings are counted. Every completed task states the check that followed it.</t>
+      <c r="B38" s="30" t="inlineStr">
+        <is>
+          <t>Seventy-five individual tasks are completed, eighty-six rows in total once the finished stage headings are counted. Every completed task states the check that followed it.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="31" t="inlineStr">
-        <is>
-          <t>Nineteen individual tasks are still open - two in progress, two awaiting review, fifteen not started - and each one states plainly what is missing and what it would take.</t>
+      <c r="B39" s="30" t="inlineStr">
+        <is>
+          <t>Eighteen individual tasks are still open - two in progress, two awaiting review, fourteen not started - and each one states plainly what is missing and what it would take.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="31" t="inlineStr">
+      <c r="B40" s="30" t="inlineStr">
         <is>
           <t>The register distinguishes work that changed the product from work that checked it: forty-five rows are development, forty are testing, verification or measurement, ten are documentation and the rest are planning, setup, tooling or coordination.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="30" t="inlineStr">
+      <c r="B42" s="29" t="inlineStr">
         <is>
           <t>What is not covered, and why</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="31" t="inlineStr">
+      <c r="B43" s="30" t="inlineStr">
         <is>
           <t>Anything before 23 October 2026. The software is older than this record, but its history was captured in a single step with no dates, so no earlier work can be dated without inventing it.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="31" t="inlineStr">
+      <c r="B44" s="30" t="inlineStr">
         <is>
           <t>Anything after 25 October 2026. No future commitment is recorded, and no open task has a promised completion date.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="31" t="inlineStr">
+      <c r="B45" s="30" t="inlineStr">
         <is>
           <t>Work that left no trace. Three early rounds were lost when the working machine was wiped and had to be rebuilt; the repairs survived, but their individual dates did not always do so.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="31" t="inlineStr">
+      <c r="B46" s="30" t="inlineStr">
         <is>
           <t>The two documents that describe how to run and develop the software have been written but not read by a human, so they appear as pending review rather than as completed documentation.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="31" t="inlineStr">
+      <c r="B47" s="30" t="inlineStr">
         <is>
           <t>Four written references, the translations into four languages, the scheduled-work feature and the scaled tests are genuinely unfinished. They are listed as open rather than quietly omitted.</t>
         </is>
